--- a/artfynd/A 25512-2022 artfynd.xlsx
+++ b/artfynd/A 25512-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25512-2022 artfynd.xlsx
+++ b/artfynd/A 25512-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111632455</v>
+        <v>111632295</v>
       </c>
       <c r="B2" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679622</v>
+        <v>679616</v>
       </c>
       <c r="R2" t="n">
-        <v>6612740</v>
+        <v>6612690</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111632126</v>
+        <v>111631628</v>
       </c>
       <c r="B3" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +794,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679401</v>
+        <v>679347</v>
       </c>
       <c r="R3" t="n">
-        <v>6612685</v>
+        <v>6612733</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,37 +891,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111631780</v>
+        <v>111631555</v>
       </c>
       <c r="B4" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679489</v>
+        <v>679347</v>
       </c>
       <c r="R4" t="n">
-        <v>6612786</v>
+        <v>6612733</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,37 +999,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111631615</v>
+        <v>111632936</v>
       </c>
       <c r="B5" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679347</v>
+        <v>679389</v>
       </c>
       <c r="R5" t="n">
-        <v>6612732</v>
+        <v>6612882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,37 +1107,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111631628</v>
+        <v>111631648</v>
       </c>
       <c r="B6" t="n">
-        <v>89183</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679347</v>
+        <v>679489</v>
       </c>
       <c r="R6" t="n">
-        <v>6612732</v>
+        <v>6612786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,37 +1215,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111631555</v>
+        <v>111632005</v>
       </c>
       <c r="B7" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679347</v>
+        <v>679445</v>
       </c>
       <c r="R7" t="n">
-        <v>6612732</v>
+        <v>6612665</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,37 +1323,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111632295</v>
+        <v>111631820</v>
       </c>
       <c r="B8" t="n">
-        <v>89419</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>5685</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1359,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679616</v>
+        <v>679445</v>
       </c>
       <c r="R8" t="n">
-        <v>6612689</v>
+        <v>6612665</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,15 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111632616</v>
+        <v>111631615</v>
       </c>
       <c r="B9" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,21 +1442,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679698</v>
+        <v>679347</v>
       </c>
       <c r="R9" t="n">
-        <v>6612862</v>
+        <v>6612733</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,15 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111632936</v>
+        <v>111631780</v>
       </c>
       <c r="B10" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,21 +1550,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>679390</v>
+        <v>679489</v>
       </c>
       <c r="R10" t="n">
-        <v>6612882</v>
+        <v>6612786</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,37 +1647,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111632005</v>
+        <v>111632126</v>
       </c>
       <c r="B11" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>679445</v>
+        <v>679401</v>
       </c>
       <c r="R11" t="n">
-        <v>6612665</v>
+        <v>6612685</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,37 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111631648</v>
+        <v>111632455</v>
       </c>
       <c r="B12" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1846,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>679489</v>
+        <v>679623</v>
       </c>
       <c r="R12" t="n">
-        <v>6612786</v>
+        <v>6612739</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,119 +1860,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>111631820</v>
-      </c>
-      <c r="B13" t="n">
-        <v>88819</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>5685</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Gullgröppa</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Pseudomerulius aureus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Lilla Vreda, Upl</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>679445</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6612665</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Vallentuna</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Frösunda</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2023-08-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Karolin Hård</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Karolin Hård</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
